--- a/measurements/33/Filled_2D_sections/sagittal/week33_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/33/Filled_2D_sections/sagittal/week33_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AF27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,97 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,34 +591,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.505353955978585</v>
+        <v>3242.063492063492</v>
       </c>
       <c r="D2" t="n">
-        <v>14.59856562498139</v>
+        <v>285.01961458297</v>
       </c>
       <c r="E2" t="n">
-        <v>12.77390268953835</v>
+        <v>249.3952429862249</v>
       </c>
       <c r="F2" t="n">
         <v>1.14284302767841</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5015126394050854</v>
+        <v>0.5015126394050855</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.310267857142857</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.205729166666666</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.755497685185184</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="S2" t="n">
+        <v>9.205729166666666</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.183035714285714</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.310267857142857</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.511904761904762</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.971075148809524</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>8.554506246281976</v>
+      <c r="AF2" s="2" t="n">
+        <v>3260.799319727891</v>
       </c>
     </row>
     <row r="3">
@@ -544,34 +668,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.505353955978585</v>
+        <v>3242.063492063492</v>
       </c>
       <c r="D3" t="n">
-        <v>14.59856562498139</v>
+        <v>285.01961458297</v>
       </c>
       <c r="E3" t="n">
-        <v>12.77390268953835</v>
+        <v>249.3952429862249</v>
       </c>
       <c r="F3" t="n">
         <v>1.14284302767841</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5015126394050854</v>
+        <v>0.5015126394050855</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.310267857142857</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9.205729166666666</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.755497685185184</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="S3" t="n">
+        <v>9.205729166666666</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6.183035714285714</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.310267857142857</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.511904761904762</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.971075148809524</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>15.46249666359367</v>
+      <c r="AF3" s="2" t="n">
+        <v>301.8868396225429</v>
       </c>
     </row>
     <row r="4">
@@ -582,43 +745,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.565734681737062</v>
+        <v>3265.079365079365</v>
       </c>
       <c r="D4" t="n">
-        <v>15.10412467979803</v>
+        <v>294.8900532722473</v>
       </c>
       <c r="E4" t="n">
-        <v>12.72512217847312</v>
+        <v>248.4428615797134</v>
       </c>
       <c r="F4" t="n">
         <v>1.186953214905035</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4718276181083133</v>
+        <v>0.4718276181083131</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5437309451219512</v>
+        <v>1.486235119047619</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5437309451219512</v>
+        <v>10.6156994047619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5437309451219512</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>4.700520833333334</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5.412946428571428</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10.6156994047619</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7.891555059523809</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.486235119047619</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.573164682539682</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>12.91411939583174</v>
+      <c r="AF4" s="2" t="n">
+        <v>252.132807251953</v>
       </c>
     </row>
     <row r="5">
@@ -629,17 +822,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.588042831647829</v>
+        <v>3273.582766439909</v>
       </c>
       <c r="D5" t="n">
-        <v>15.25638425059435</v>
+        <v>297.8627401306516</v>
       </c>
       <c r="E5" t="n">
-        <v>12.79410825124601</v>
+        <v>249.7897325243269</v>
       </c>
       <c r="F5" t="n">
         <v>1.192453897606231</v>
@@ -648,23 +841,53 @@
         <v>0.4636612790861426</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.513719512195122</v>
+        <v>2.855282738095238</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5463033536585366</v>
+        <v>10.66592261904762</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5300114329268293</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>5.755673363095238</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6.123511904761904</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10.66592261904762</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8.285900297619047</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.855282738095238</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.225446428571429</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AF5" s="2" t="n">
         <v>1.197329471492512</v>
       </c>
     </row>
@@ -676,17 +899,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.588042831647829</v>
+        <v>3273.582766439909</v>
       </c>
       <c r="D6" t="n">
-        <v>15.25638425059435</v>
+        <v>297.8627401306516</v>
       </c>
       <c r="E6" t="n">
-        <v>12.79410825124601</v>
+        <v>249.7897325243269</v>
       </c>
       <c r="F6" t="n">
         <v>1.192453897606231</v>
@@ -695,23 +918,53 @@
         <v>0.4636612790861426</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.513719512195122</v>
+        <v>2.855282738095238</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5463033536585366</v>
+        <v>10.66592261904762</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5300114329268293</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>5.755673363095238</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6.123511904761904</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10.66592261904762</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8.285900297619047</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.855282738095238</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.225446428571429</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AF6" s="2" t="n">
         <v>0.4512011136161115</v>
       </c>
     </row>
@@ -723,17 +976,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.613920285544319</v>
+        <v>3283.44671201814</v>
       </c>
       <c r="D7" t="n">
-        <v>15.34312445942949</v>
+        <v>299.5562394460042</v>
       </c>
       <c r="E7" t="n">
-        <v>12.78573881416786</v>
+        <v>249.6263292289916</v>
       </c>
       <c r="F7" t="n">
         <v>1.200018605293875</v>
@@ -742,24 +995,54 @@
         <v>0.4598149596903215</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5190548780487805</v>
+        <v>2.680431547619047</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5437309451219512</v>
+        <v>10.6156994047619</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5313929115853658</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>5.932152157738095</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6.42485119047619</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10.6156994047619</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8.488188244047619</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.680431547619047</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.042038690476191</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.376116071428571</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>1.35</v>
+      <c r="AF7" s="2" t="n">
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -770,43 +1053,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.625520523497919</v>
+        <v>3287.868480725623</v>
       </c>
       <c r="D8" t="n">
-        <v>15.05289287392686</v>
+        <v>293.8898132528577</v>
       </c>
       <c r="E8" t="n">
-        <v>12.98432751399715</v>
+        <v>253.5035371780396</v>
       </c>
       <c r="F8" t="n">
-        <v>1.159312475574865</v>
+        <v>1.159312475574864</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4783604161625928</v>
+        <v>0.4783604161625929</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5198170731707318</v>
+        <v>2.587425595238095</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5435403963414634</v>
+        <v>10.61197916666667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5316787347560976</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>6.03213355654762</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.47172619047619</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10.61197916666667</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7.716517857142857</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.123883928571428</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.963169642857143</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.587425595238095</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6315157096883469</v>
+      <c r="AF8" s="2" t="n">
+        <v>1.952752976190476</v>
       </c>
     </row>
     <row r="9">
@@ -817,43 +1130,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.625520523497919</v>
+        <v>3287.868480725623</v>
       </c>
       <c r="D9" t="n">
-        <v>15.05289287392686</v>
+        <v>293.8898132528577</v>
       </c>
       <c r="E9" t="n">
-        <v>12.98432751399715</v>
+        <v>253.5035371780396</v>
       </c>
       <c r="F9" t="n">
-        <v>1.159312475574865</v>
+        <v>1.159312475574864</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4783604161625928</v>
+        <v>0.4783604161625929</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5198170731707318</v>
+        <v>2.587425595238095</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5435403963414634</v>
+        <v>10.61197916666667</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5316787347560976</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>6.03213355654762</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.47172619047619</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10.61197916666667</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.716517857142857</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.123883928571428</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.963169642857143</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.587425595238095</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.6626810213414634</v>
+      <c r="AF9" s="2" t="n">
+        <v>12.56482514880952</v>
       </c>
     </row>
     <row r="10">
@@ -864,43 +1207,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.56484235574063</v>
+        <v>3264.739229024943</v>
       </c>
       <c r="D10" t="n">
-        <v>16.44588550416435</v>
+        <v>321.0863360336849</v>
       </c>
       <c r="E10" t="n">
-        <v>12.90350530787212</v>
+        <v>251.9255798203604</v>
       </c>
       <c r="F10" t="n">
         <v>1.274528518551552</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3979373587121312</v>
+        <v>0.3979373587121313</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.540110518292683</v>
+        <v>1.497395833333333</v>
       </c>
       <c r="J10" t="n">
-        <v>0.633765243902439</v>
+        <v>12.3735119047619</v>
       </c>
       <c r="K10" t="n">
-        <v>0.586937881097561</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>5.951218377976191</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4.709821428571428</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12.3735119047619</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8.099702380952381</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.640252976190476</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.973586309523809</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.497395833333333</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.6470983655149052</v>
+      <c r="AF10" s="2" t="n">
+        <v>5.554041994401927</v>
       </c>
     </row>
     <row r="11">
@@ -911,17 +1284,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.57584770969661</v>
+        <v>3268.934240362812</v>
       </c>
       <c r="D11" t="n">
-        <v>16.51385616383902</v>
+        <v>322.4133822463808</v>
       </c>
       <c r="E11" t="n">
-        <v>12.93208023687688</v>
+        <v>252.4834712914058</v>
       </c>
       <c r="F11" t="n">
         <v>1.27696827280335</v>
@@ -930,16 +1303,54 @@
         <v>0.3951754250577758</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5453506097560976</v>
+        <v>1.696428571428571</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6551067073170732</v>
+        <v>12.79017857142857</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6002286585365855</v>
+        <v>6.065383184523808</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5.245535714285714</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12.79017857142857</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8.274553571428571</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.660714285714286</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.793154761904762</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.696428571428571</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="12">
@@ -950,17 +1361,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.57584770969661</v>
+        <v>3268.934240362812</v>
       </c>
       <c r="D12" t="n">
-        <v>16.51385616383902</v>
+        <v>322.4133822463808</v>
       </c>
       <c r="E12" t="n">
-        <v>12.93208023687688</v>
+        <v>252.4834712914058</v>
       </c>
       <c r="F12" t="n">
         <v>1.27696827280335</v>
@@ -969,16 +1380,54 @@
         <v>0.3951754250577758</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5453506097560976</v>
+        <v>1.696428571428571</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6551067073170732</v>
+        <v>12.79017857142857</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6002286585365855</v>
+        <v>6.065383184523808</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5.245535714285714</v>
+      </c>
+      <c r="S12" t="n">
+        <v>12.79017857142857</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8.274553571428571</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.660714285714286</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.793154761904762</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.696428571428571</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>18.68923611111111</v>
       </c>
     </row>
     <row r="13">
@@ -989,17 +1438,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.556811421772755</v>
+        <v>3261.678004535147</v>
       </c>
       <c r="D13" t="n">
-        <v>15.89644862093577</v>
+        <v>310.3592349801744</v>
       </c>
       <c r="E13" t="n">
-        <v>12.95473715735645</v>
+        <v>252.9258206912449</v>
       </c>
       <c r="F13" t="n">
         <v>1.227076121101295</v>
@@ -1008,16 +1457,54 @@
         <v>0.4255215934100005</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5217225609756098</v>
+        <v>1.901041666666667</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6322408536585367</v>
+        <v>12.34375</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5769817073170732</v>
+        <v>6.051897321428571</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5.357142857142857</v>
+      </c>
+      <c r="S13" t="n">
+        <v>12.34375</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8.154017857142858</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.681175595238095</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.062872023809524</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.901041666666667</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="14">
@@ -1028,35 +1515,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.555324211778704</v>
+        <v>3261.111111111111</v>
       </c>
       <c r="D14" t="n">
-        <v>15.69540862630053</v>
+        <v>306.4341684182485</v>
       </c>
       <c r="E14" t="n">
-        <v>12.92616223998186</v>
+        <v>252.3679294472649</v>
       </c>
       <c r="F14" t="n">
         <v>1.214235775082037</v>
       </c>
       <c r="G14" t="n">
-        <v>0.436416419930376</v>
+        <v>0.4364164199303761</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6187118902439025</v>
+        <v>1.300223214285714</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6187118902439025</v>
+        <v>12.07961309523809</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6187118902439025</v>
+        <v>5.761253720238095</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5.319940476190476</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12.07961309523809</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.840401785714285</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.212425595238095</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.375372023809524</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.300223214285714</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>5.017981150793651</v>
       </c>
     </row>
     <row r="15">
@@ -1067,35 +1592,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.555324211778704</v>
+        <v>3261.111111111111</v>
       </c>
       <c r="D15" t="n">
-        <v>15.69540862630053</v>
+        <v>306.4341684182485</v>
       </c>
       <c r="E15" t="n">
-        <v>12.92616223998186</v>
+        <v>252.3679294472649</v>
       </c>
       <c r="F15" t="n">
         <v>1.214235775082037</v>
       </c>
       <c r="G15" t="n">
-        <v>0.436416419930376</v>
+        <v>0.4364164199303761</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6187118902439025</v>
+        <v>1.300223214285714</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6187118902439025</v>
+        <v>12.07961309523809</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6187118902439025</v>
+        <v>5.761253720238095</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5.319940476190476</v>
+      </c>
+      <c r="S15" t="n">
+        <v>12.07961309523809</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7.840401785714285</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.212425595238095</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.375372023809524</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.300223214285714</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>4.749503968253967</v>
       </c>
     </row>
     <row r="16">
@@ -1106,35 +1669,70 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.544616299821536</v>
+        <v>3257.02947845805</v>
       </c>
       <c r="D16" t="n">
-        <v>15.42293124954875</v>
+        <v>301.1143720149994</v>
       </c>
       <c r="E16" t="n">
-        <v>12.93208026304478</v>
+        <v>252.4834718023027</v>
       </c>
       <c r="F16" t="n">
         <v>1.192610232525538</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4514073061965477</v>
+        <v>0.4514073061965476</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6399580792682927</v>
+        <v>2.165178571428571</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6399580792682927</v>
+        <v>12.49441964285714</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6399580792682927</v>
+        <v>5.867125496031746</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5.455729166666666</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12.49441964285714</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7.501860119047619</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.030133928571428</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.165178571428571</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>4.840029761904762</v>
       </c>
     </row>
     <row r="17">
@@ -1145,35 +1743,73 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.56365258774539</v>
+        <v>3264.285714285714</v>
       </c>
       <c r="D17" t="n">
-        <v>15.22434257588736</v>
+        <v>297.2371645768483</v>
       </c>
       <c r="E17" t="n">
-        <v>12.99514821971335</v>
+        <v>253.7147985753559</v>
       </c>
       <c r="F17" t="n">
         <v>1.17154051023384</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4642926502109045</v>
+        <v>0.4642926502109047</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6678734756097561</v>
+        <v>1.380208333333333</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6678734756097561</v>
+        <v>13.03943452380952</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6678734756097561</v>
+        <v>5.224277210884353</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.944196428571428</v>
+      </c>
+      <c r="S17" t="n">
+        <v>13.03943452380952</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7.280970982142857</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3.506324404761905</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.559523809523809</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.380208333333333</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>5.184808298319328</v>
       </c>
     </row>
     <row r="18">
@@ -1184,35 +1820,73 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.56365258774539</v>
+        <v>3264.285714285714</v>
       </c>
       <c r="D18" t="n">
-        <v>15.22434257588736</v>
+        <v>297.2371645768483</v>
       </c>
       <c r="E18" t="n">
-        <v>12.99514821971335</v>
+        <v>253.7147985753559</v>
       </c>
       <c r="F18" t="n">
         <v>1.17154051023384</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4642926502109045</v>
+        <v>0.4642926502109047</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6678734756097561</v>
+        <v>1.380208333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6678734756097561</v>
+        <v>13.03943452380952</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6678734756097561</v>
+        <v>5.224277210884353</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.944196428571428</v>
+      </c>
+      <c r="S18" t="n">
+        <v>13.03943452380952</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7.280970982142857</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3.506324404761905</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.559523809523809</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.380208333333333</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>11.48404674369748</v>
       </c>
     </row>
     <row r="19">
@@ -1223,17 +1897,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.532718619869126</v>
+        <v>3252.49433106576</v>
       </c>
       <c r="D19" t="n">
-        <v>15.78460015901705</v>
+        <v>308.1755269141424</v>
       </c>
       <c r="E19" t="n">
-        <v>12.9724913399394</v>
+        <v>253.2724499702454</v>
       </c>
       <c r="F19" t="n">
         <v>1.216774769424575</v>
@@ -1242,16 +1916,57 @@
         <v>0.430358235189538</v>
       </c>
       <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="J19" t="n">
+        <v>18.58816964285714</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.428059895833334</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.9520769817073171</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.9520769817073171</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.9520769817073171</v>
+      <c r="M19" t="n">
+        <v>18.58816964285714</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5.143229166666666</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.944196428571428</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.840029761904762</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.102678571428571</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.477213541666667</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>7.723416710434172</v>
       </c>
     </row>
     <row r="20">
@@ -1262,17 +1977,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.488994646044022</v>
+        <v>3235.827664399093</v>
       </c>
       <c r="D20" t="n">
-        <v>15.43721871259736</v>
+        <v>301.3933177221389</v>
       </c>
       <c r="E20" t="n">
-        <v>13.05821621417999</v>
+        <v>254.9461260863713</v>
       </c>
       <c r="F20" t="n">
         <v>1.182184339682934</v>
@@ -1281,16 +1996,54 @@
         <v>0.4476390951916152</v>
       </c>
       <c r="H20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.964285714285714</v>
+      </c>
+      <c r="J20" t="n">
+        <v>18.64769345238095</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.196010044642857</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.955125762195122</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.955125762195122</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.955125762195122</v>
+      <c r="M20" t="n">
+        <v>18.64769345238095</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5.091145833333333</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.88095238095238</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.964285714285714</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.723958333333333</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.589657738095238</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>3.65</v>
       </c>
     </row>
     <row r="21">
@@ -1301,35 +2054,73 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.395002974419988</v>
+        <v>3200</v>
       </c>
       <c r="D21" t="n">
-        <v>15.13269965532349</v>
+        <v>295.4479456515539</v>
       </c>
       <c r="E21" t="n">
-        <v>13.1390383388938</v>
+        <v>256.5240818545932</v>
       </c>
       <c r="F21" t="n">
         <v>1.151735710407977</v>
       </c>
       <c r="G21" t="n">
-        <v>0.460678446118007</v>
+        <v>0.4606784461180069</v>
       </c>
       <c r="H21" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.396949404761905</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18.83184523809524</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.76541832010582</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.9645579268292683</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.9645579268292683</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.9645579268292683</v>
+      <c r="M21" t="n">
+        <v>18.83184523809524</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.819568452380953</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.423363095238095</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.396949404761905</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.011532738095238</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.468998015873016</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>3.578023538961038</v>
       </c>
     </row>
     <row r="22">
@@ -1339,7 +2130,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>2.325825216450216</v>
       </c>
     </row>
     <row r="23">
@@ -1353,6 +2152,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>1.732700892857143</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1362,6 +2169,70 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>2.173652447089947</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>3.59250992063492</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>2.875354800485009</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/33/Filled_2D_sections/sagittal/week33_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/33/Filled_2D_sections/sagittal/week33_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2238,4 +2444,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week33_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3260.799319727891</v>
+      </c>
+      <c r="D10" t="n">
+        <v>20.00273161190924</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3287.868480725623</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>301.8868396225429</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10.84145919014866</v>
+      </c>
+      <c r="E11" t="n">
+        <v>285.01961458297</v>
+      </c>
+      <c r="F11" t="n">
+        <v>322.4133822463808</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.197329471492512</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.04175753772512499</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.14284302767841</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.27696827280335</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4512011136161114</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03115248149525277</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3951754250577758</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5015126394050855</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0115.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0115.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0116.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0117.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0117.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0118.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0119.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0119.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0120.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0121.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0121.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0122.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0123.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0123.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0125.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0125.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0126.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.8255779474818965</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3663475485325233</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.9665456669582609</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.039989878493258</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>18.68923611111111</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.1270385504460704</v>
+      </c>
+      <c r="E48" t="n">
+        <v>18.58816964285714</v>
+      </c>
+      <c r="F48" t="n">
+        <v>18.83184523809524</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>85</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7.477853641456583</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.400843792985915</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13.03943452380952</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>73</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.71857672863666</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7466055360697805</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.300223214285714</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.123883928571428</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>